--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_024_Angola.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_024_Angola.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re12a25d101f54507"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Re2b4219862954128"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb3b9f9cd2ae74028"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rfacd0d3948ea47c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rd2b71deda72248de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rdfeb11451dfd45eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rd21f57825714467c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R69319846bccd455e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R65c3721677134608"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R00189d7e644148c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R4bc9cf4f190a4570"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rf4ebfbdfccd0490a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ024CommercialTable" displayName="EEZ024CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ024CommercialTable" displayName="EEZ024CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ024FunctionalTable" displayName="EEZ024FunctionalTable" ref="A1:O23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O23"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ024FunctionalTable" displayName="EEZ024FunctionalTable" ref="A1:E23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E23"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ024ValidationTable" displayName="EEZ024ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ024ValidationTable" displayName="EEZ024ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -8734,7 +8688,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0fd520ab8b3d472c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e84b158f22e45a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8744,20 +8698,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8765,606 +8709,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>12522.0648222317</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.444893474717754</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>2785.4378628083437</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>12522.0648222317</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>2802.7787220264318</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$121,A2,'Species'!$U$2:$U$121))</x:f>
-        <x:v>35096576.8395867</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.444893474717754</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>2785.4378628083437</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>34879433.47638461</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>217143.36320208758</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0062255415744956</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.006225541574495646</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2168.3382436945003</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.435595346377362</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>272.643624362085</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2168.3382436945003</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>393.51766914047016</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$121,A3,'Species'!$U$2:$U$121))</x:f>
-        <x:v>853279.4115668006</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.435595346377362</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>272.643624362085</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>591183.5976037865</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>262095.81396301405</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.4433408082114478</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.44334080821144783</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>17609.7235197956</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.513285678210124</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>326.0511063687083</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>17609.7235197956</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>333.0800549446042</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$121,A4,'Species'!$U$2:$U$121))</x:f>
-        <x:v>5865447.677532808</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.513285678210124</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>326.0511063687083</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>5741669.836476419</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>123777.8410563888</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0215578123754239</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.021557812375423785</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>207170.3290474219</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.814896252965661</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>65.29745472920558</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>207170.3290474219</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>70.01292373766748</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$121,A5,'Species'!$U$2:$U$121))</x:f>
-        <x:v>14504600.448304627</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.814896252965661</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>65.29745472920558</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>13527695.182208655</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>976905.2660959717</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.072215203915947</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.07221520391594699</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>258.4002015359</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.0339773827964693</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>10.813776338084855</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>258.4002015359</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>10.879760783226379</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$121,A6,'Species'!$U$2:$U$121))</x:f>
-        <x:v>2811.3323790480777</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.0339773827964693</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>10.813776338084855</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2794.2819851252734</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>17.050393922804233</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0061018873591028</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.006101887359102674</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>209568.68603541632</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.320926384623894</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>209.3757522003457</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>209568.68603541632</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>270.73217772106887</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$121,A7,'Species'!$U$2:$U$121))</x:f>
-        <x:v>56736986.75251122</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.320926384623894</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>209.3757522003457</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>43878601.27630337</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>12858385.476207845</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.2930445616358335</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.2930445616358335</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>157574.8295160107</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.645481836140419</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>442.0606278194284</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>157574.8295160107</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>630.3123035634719</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$121,A8,'Species'!$U$2:$U$121))</x:f>
-        <x:v>99321353.77585807</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.645481836140419</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>442.0606278194284</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>69657628.0643871</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>29663725.711470976</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4258503560306663</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.4258503560306663</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>37.713219298</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9329066789154163</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>856.8537049472545</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>37.713219298</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>978.2772694582146</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$121,A9,'Species'!$U$2:$U$121))</x:f>
-        <x:v>36893.985197326285</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9329066789154163</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>856.8537049472545</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>32314.711680979595</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>4579.27351634669</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1417086298511536</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.14170862985115368</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>5201.058814432799</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.795818976488502</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>624.912161320519</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>5201.058814432799</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>814.9074011487457</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$121,A10,'Species'!$U$2:$U$121))</x:f>
-        <x:v>4238381.321691209</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.795818976488502</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>624.912161320519</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>3250204.9048823365</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>988176.416808873</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.304035113393765</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.30403511339376516</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>7625.8635972683005</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.451320732566084</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2826.9669589361765</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>7625.8635972683005</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2837.0179682120493</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$121,A11,'Species'!$U$2:$U$121))</x:f>
-        <x:v>21634712.048584342</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.451320732566084</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2826.9669589361765</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>21558064.42283166</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>76647.62575268373</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0035554038734344</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.003555403873434387</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f6f4436267944d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc756703312564099"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9374,20 +8924,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -9395,1254 +8935,440 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1967.7161907838997</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.020885171672616</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1049.2649642231588</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1967.7161907838997</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1132.557425751491</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$121,A2,'Species'!$U$2:$U$121))</x:f>
-        <x:v>2228551.5836437433</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.020885171672616</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1049.2649642231588</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2064655.658524199</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>163895.92511954438</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0793817237479184</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.07938172374791834</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>11526.4601442161</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.46</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2884.031503126606</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>11526.4601442161</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2884.031503126606</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$121,A3,'Species'!$U$2:$U$121))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>33242674.175452475</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.46</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2884.031503126606</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>33242674.175452475</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>21.906242931799998</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>21.906242931799998</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$121,A4,'Species'!$U$2:$U$121))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>47925.637611108155</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>47925.637611108155</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>25457.1975164449</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.239828156322562</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1737.1133435898269</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>25457.1975164449</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1952.2017641918708</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$121,A5,'Species'!$U$2:$U$121))</x:f>
-        <x:v>49697585.90298464</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.239828156322562</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1737.1133435898269</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>44222037.496218234</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>5475548.406766407</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1238194510425863</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.12381945104258625</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>4291.860783040301</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.790049075012421</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>616.6646806585835</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>4291.860783040301</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>616.6755252134924</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$121,A6,'Species'!$U$2:$U$121))</x:f>
-        <x:v>2646685.5025245682</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.790049075012421</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>616.6646806585835</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2646638.9592046454</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>46.54331992287189</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0000175858213531</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.00001758582135315459</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>7001.3962700094</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.445527309779737</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2789.506063590489</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>7001.3962700094</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2797.3851177126635</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$121,A7,'Species'!$U$2:$U$121))</x:f>
-        <x:v>19585601.72893325</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.445527309779737</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2789.506063590489</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>19530437.34879105</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>55164.38014219701</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0028245337857533</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.0028245337857532274</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>2464.6184524179002</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.5100840781161797</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>323.65630976082275</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>2464.6184524179002</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>364.30268431303665</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$121,A8,'Species'!$U$2:$U$121))</x:f>
-        <x:v>897867.1180232832</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.5100840781161797</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>323.65630976082275</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>797689.3132780076</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>100177.80474527564</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1255849903938253</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.12558499039382526</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>21.806923718500002</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.60059804607584</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>398.6557624537141</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>21.806923718500002</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>416.2922148232023</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$121,A9,'Species'!$U$2:$U$121))</x:f>
-        <x:v>9078.052573254989</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.60059804607584</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>398.6557624537141</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>8693.4558017686</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>384.5967714863891</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0442398029340814</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.04423980293408136</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>2736.0683981561</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.0531819555927875</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1130.2693624465514</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>2736.0683981561</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1220.790777397223</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$121,A10,'Species'!$U$2:$U$121))</x:f>
-        <x:v>3340167.0667969603</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.0531819555927875</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1130.2693624465514</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>3092494.2839940526</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>247672.78280290775</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0800883558895478</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.08008835588954773</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>701.9790124598</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.8511127105761855</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>70.97619455234064</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>701.9790124598</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>71.18273208264108</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$121,A11,'Species'!$U$2:$U$121))</x:f>
-        <x:v>49968.7839715629</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.8511127105761855</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>70.97619455234064</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>49823.798960006716</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>144.98501155618578</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0029099549729752</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0029099549729751525</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1024.6695251095998</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.245848594383067</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1761.3618857785646</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1024.6695251095998</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1816.876425064525</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$121,A12,'Species'!$U$2:$U$121))</x:f>
-        <x:v>1861697.903653694</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.245848594383067</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1761.3618857785646</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1804813.847046871</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>56884.05660682311</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0315179633067975</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.03151796330679739</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1.8186818973999999</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.249983719592171</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1778.2127488848053</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1.8186818973999999</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1778.224246752363</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$121,A13,'Species'!$U$2:$U$121))</x:f>
-        <x:v>3234.0242470862727</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.249983719592171</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1778.2127488848053</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>3234.003336122687</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0.02091096358572031</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0000064659684647</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.000006465968464581392</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>98072.06609572761</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.53728516319792</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>344.57610948986706</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>98072.06609572761</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>447.8937484758917</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$121,A14,'Species'!$U$2:$U$121))</x:f>
-        <x:v>43925865.30439085</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.53728516319792</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>344.57610948986706</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>33793290.98489892</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>10132574.31949193</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.2998398209875397</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.2998398209875397</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>218040.74277293158</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.3073731905999995</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>202.94258624299368</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>218040.74277293158</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>208.83621730837734</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$121,A15,'Species'!$U$2:$U$121))</x:f>
-        <x:v>45534803.939807944</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.3073731905999995</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>202.94258624299368</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>44249752.244682066</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1285051.6951258779</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0290408788736285</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.02904087887362839</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>16756.8307353223</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.2691398355486596</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>185.84027333202837</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>16756.8307353223</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>423.6368852018861</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$121,A16,'Species'!$U$2:$U$121))</x:f>
-        <x:v>7098811.57856717</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.2691398355486596</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>185.84027333202837</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>3114094.00403083</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>3984717.5745363394</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>2.2795752374137033</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>1.2795752374137033</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>6534.970308552099</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.8566195630179774</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>718.8190249117544</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>6534.970308552099</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>865.1367301659898</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$121,A17,'Species'!$U$2:$U$121))</x:f>
-        <x:v>5653642.844472592</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.8566195630179774</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>718.8190249117544</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>4697460.985020686</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>956181.8594519058</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.2035529113495542</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.20355291134955433</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>258.4002015359</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.0339773827964693</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>10.813776338084855</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>258.4002015359</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>10.879760783226379</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$121,A18,'Species'!$U$2:$U$121))</x:f>
-        <x:v>2811.3323790480777</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.0339773827964693</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>10.813776338084855</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>2794.2819851252734</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>17.050393922804233</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0061018873591028</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.006101887359102674</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>1466.3592312347</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.7154002773519754</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>519.2784231657517</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>1466.3592312347</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>547.8266242568925</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$121,A19,'Species'!$U$2:$U$121))</x:f>
-        <x:v>803310.6275952377</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.7154002773519754</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>519.2784231657517</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>761448.7093900989</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>41861.91820513876</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0549766749735108</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.05497667497351082</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>4982.66761763</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.426315235799989</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>266.8795125940332</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>4982.66761763</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>416.01531368880325</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$121,A20,'Species'!$U$2:$U$121))</x:f>
-        <x:v>2072866.0319553863</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.426315235799989</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>266.8795125940332</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>1329771.905211167</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>743094.1267442193</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.5588132249088362</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.5588132249088361</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>198797.3764293314</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>2.812060774021785</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>64.87252080874977</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>198797.3764293314</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>69.02555700528816</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$121,A21,'Species'!$U$2:$U$121))</x:f>
-        <x:v>13722099.639224544</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>2.812060774021785</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>64.87252080874977</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>12896486.939136662</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>825612.7000878826</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0640184186580623</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.06401841865806225</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>17609.7235197956</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.513285678210124</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>326.0511063687083</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>17609.7235197956</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>333.0800549446042</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$121,A22,'Species'!$U$2:$U$121))</x:f>
-        <x:v>5865447.677532808</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.513285678210124</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>326.0511063687083</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>5741669.836476419</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>123777.8410563888</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0215578123754239</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.021557812375423785</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>0.3719638588</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.97</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>933.2543007969915</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>0.3719638588</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>933.2543007969916</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$121,A23,'Species'!$U$2:$U$121))</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>347.1368709661449</x:v>
       </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.97</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>933.2543007969915</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
-        <x:v>347.1368709661449</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G23">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O23">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0d3f05b2a4d48b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R531c5b1df2574ba5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10817,7 +9543,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -10916,7 +9642,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>238291043.5932122</x:v>
+        <x:v>193119589.75474402</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10930,7 +9656,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>238291043.59321222</x:v>
+        <x:v>214098235.0059215</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10944,7 +9670,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-45171453.838468164</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10958,7 +9684,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>2.9802322387695312e-8</x:v>
+        <x:v>-24192808.587290674</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10969,9 +9695,9 @@
         <x:v>EEZ_024</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -10983,47 +9709,19 @@
         <x:v>EEZ_024</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_024</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_024</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43e05f548cc04fb2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb168f010cccf42eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11070,7 +9768,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
